--- a/SAP Reports/Annual Financial Data/Aggregate P&L Output.xlsx
+++ b/SAP Reports/Annual Financial Data/Aggregate P&L Output.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -808,13 +808,13 @@
         </is>
       </c>
       <c r="C7" s="20" t="n">
-        <v>0</v>
+        <v>1858364.25</v>
       </c>
       <c r="D7" s="20" t="n">
-        <v>0</v>
+        <v>1640834.72</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>200456.92</v>
+        <v>898497.73</v>
       </c>
       <c r="F7" s="20" t="n">
         <v>0</v>
@@ -859,13 +859,13 @@
         </is>
       </c>
       <c r="C8" s="20" t="n">
-        <v>0</v>
+        <v>-1265003.14</v>
       </c>
       <c r="D8" s="20" t="n">
-        <v>0</v>
+        <v>-1072556.73</v>
       </c>
       <c r="E8" s="20" t="n">
-        <v>-8185.92</v>
+        <v>-51022.43</v>
       </c>
       <c r="F8" s="20" t="n">
         <v>0</v>
@@ -910,13 +910,13 @@
         </is>
       </c>
       <c r="C9" s="20" t="n">
-        <v>-117764.65</v>
+        <v>-224269.83</v>
       </c>
       <c r="D9" s="20" t="n">
-        <v>-175096.25</v>
+        <v>-264679.16</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>0</v>
+        <v>-106813.86</v>
       </c>
       <c r="F9" s="20" t="n">
         <v>-1800</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="C10" s="20" t="n">
-        <v>-158601.03</v>
+        <v>329164.9</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>-178282.4</v>
+        <v>289650.96</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>192271</v>
+        <v>330661.44</v>
       </c>
       <c r="F10" s="20" t="n">
         <v>-1800</v>
@@ -979,7 +979,7 @@
         <v>-4816.5</v>
       </c>
       <c r="I10" s="20" t="n">
-        <v>-261125.88</v>
+        <v>-372961.04</v>
       </c>
       <c r="J10" s="20" t="n">
         <v>-9615.209999999999</v>
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="C11" s="24" t="n">
-        <v>-158601.03</v>
+        <v>329164.9</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-179702.4</v>
+        <v>286810.96</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>192271</v>
+        <v>330661.44</v>
       </c>
       <c r="F11" s="24" t="n">
         <v>-1800</v>
@@ -1030,7 +1030,7 @@
         <v>-4816.5</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>-261125.88</v>
+        <v>-372961.04</v>
       </c>
       <c r="J11" s="24" t="n">
         <v>-9615.209999999999</v>

--- a/SAP Reports/Annual Financial Data/Aggregate P&L Output.xlsx
+++ b/SAP Reports/Annual Financial Data/Aggregate P&L Output.xlsx
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="C2" s="20" t="n">
-        <v>1728293.93</v>
+        <v>1709058.79</v>
       </c>
       <c r="D2" s="20" t="n">
-        <v>1540902.4</v>
+        <v>1501116.46</v>
       </c>
       <c r="E2" s="20" t="n">
         <v>819284.55</v>
@@ -584,9 +584,11 @@
         <v>403735</v>
       </c>
       <c r="J2" s="20" t="n">
-        <v>208200</v>
-      </c>
-      <c r="K2" s="18" t="n"/>
+        <v>210825</v>
+      </c>
+      <c r="K2" s="20" t="n">
+        <v>27500</v>
+      </c>
       <c r="L2" s="21">
         <f>C2+D2</f>
         <v/>
@@ -615,7 +617,7 @@
         <v>-1596475.51</v>
       </c>
       <c r="D3" s="20" t="n">
-        <v>-1201535.71</v>
+        <v>-1203949.71</v>
       </c>
       <c r="E3" s="20" t="n">
         <v>-289398.07</v>
@@ -633,9 +635,11 @@
         <v>0</v>
       </c>
       <c r="J3" s="20" t="n">
-        <v>-50276.35</v>
-      </c>
-      <c r="K3" s="18" t="n"/>
+        <v>-49127.35</v>
+      </c>
+      <c r="K3" s="20" t="n">
+        <v>0</v>
+      </c>
       <c r="L3" s="21">
         <f>C3+D3</f>
         <v/>
@@ -682,9 +686,11 @@
         <v>-1894.6</v>
       </c>
       <c r="J4" s="20" t="n">
-        <v>-34428.54</v>
-      </c>
-      <c r="K4" s="18" t="n"/>
+        <v>-35577.54</v>
+      </c>
+      <c r="K4" s="20" t="n">
+        <v>-14805.15</v>
+      </c>
       <c r="L4" s="21">
         <f>C4+D4</f>
         <v/>
@@ -710,10 +716,10 @@
         </is>
       </c>
       <c r="C5" s="20" t="n">
-        <v>-267938.18</v>
+        <v>-287173.32</v>
       </c>
       <c r="D5" s="20" t="n">
-        <v>242720.25</v>
+        <v>200520.31</v>
       </c>
       <c r="E5" s="20" t="n">
         <v>26739.89</v>
@@ -731,9 +737,11 @@
         <v>72599.49000000001</v>
       </c>
       <c r="J5" s="20" t="n">
-        <v>112699.88</v>
-      </c>
-      <c r="K5" s="18" t="n"/>
+        <v>115324.88</v>
+      </c>
+      <c r="K5" s="20" t="n">
+        <v>12694.85</v>
+      </c>
       <c r="L5" s="21">
         <f>C5+D5</f>
         <v/>
@@ -759,10 +767,10 @@
         </is>
       </c>
       <c r="C6" s="24" t="n">
-        <v>-267938.18</v>
+        <v>-287173.32</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>240306.25</v>
+        <v>200520.31</v>
       </c>
       <c r="E6" s="24" t="n">
         <v>6739.89</v>
@@ -780,9 +788,11 @@
         <v>72599.49000000001</v>
       </c>
       <c r="J6" s="24" t="n">
-        <v>112699.88</v>
-      </c>
-      <c r="K6" s="22" t="n"/>
+        <v>115324.88</v>
+      </c>
+      <c r="K6" s="24" t="n">
+        <v>12694.85</v>
+      </c>
       <c r="L6" s="25">
         <f>C6+D6</f>
         <v/>
@@ -808,31 +818,31 @@
         </is>
       </c>
       <c r="C7" s="20" t="n">
-        <v>1858364.25</v>
+        <v>1828479.87</v>
       </c>
       <c r="D7" s="20" t="n">
-        <v>1640834.72</v>
+        <v>1604546.24</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>898497.73</v>
+        <v>933000.14</v>
       </c>
       <c r="F7" s="20" t="n">
-        <v>0</v>
+        <v>389340.08</v>
       </c>
       <c r="G7" s="20" t="n">
-        <v>0</v>
+        <v>163039.36</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="I7" s="20" t="n">
-        <v>0</v>
+        <v>413052</v>
       </c>
       <c r="J7" s="20" t="n">
-        <v>12408.18</v>
+        <v>65872.02</v>
       </c>
       <c r="K7" s="20" t="n">
-        <v>0</v>
+        <v>27500</v>
       </c>
       <c r="L7" s="21">
         <f>C7+D7</f>
@@ -862,13 +872,13 @@
         <v>-1265003.14</v>
       </c>
       <c r="D8" s="20" t="n">
-        <v>-1072556.73</v>
+        <v>-1075396.73</v>
       </c>
       <c r="E8" s="20" t="n">
-        <v>-51022.43</v>
+        <v>-260083.17</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>0</v>
+        <v>-998.3099999999999</v>
       </c>
       <c r="G8" s="20" t="n">
         <v>0</v>
@@ -880,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="20" t="n">
-        <v>-1425.05</v>
+        <v>-125157.67</v>
       </c>
       <c r="K8" s="20" t="n">
         <v>0</v>
@@ -910,31 +920,31 @@
         </is>
       </c>
       <c r="C9" s="20" t="n">
-        <v>-224269.83</v>
+        <v>-229565.1</v>
       </c>
       <c r="D9" s="20" t="n">
-        <v>-264679.16</v>
+        <v>-271919.72</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>-106813.86</v>
+        <v>-136349.46</v>
       </c>
       <c r="F9" s="20" t="n">
-        <v>-1800</v>
+        <v>-7941.53</v>
       </c>
       <c r="G9" s="20" t="n">
-        <v>-33859.76</v>
+        <v>-89908.09</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>0</v>
+        <v>-41691.87</v>
       </c>
       <c r="I9" s="20" t="n">
-        <v>0</v>
+        <v>-1728.66</v>
       </c>
       <c r="J9" s="20" t="n">
-        <v>-10668.34</v>
+        <v>-13551.74</v>
       </c>
       <c r="K9" s="20" t="n">
-        <v>-764.9299999999999</v>
+        <v>-17254.15</v>
       </c>
       <c r="L9" s="21">
         <f>C9+D9</f>
@@ -961,31 +971,31 @@
         </is>
       </c>
       <c r="C10" s="20" t="n">
-        <v>329164.9</v>
+        <v>293985.25</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>289650.96</v>
+        <v>243281.92</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>330661.44</v>
+        <v>126567.51</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>-1800</v>
+        <v>100400.24</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>-43103.44</v>
+        <v>63887.59</v>
       </c>
       <c r="H10" s="20" t="n">
-        <v>-4816.5</v>
+        <v>-49638.12</v>
       </c>
       <c r="I10" s="20" t="n">
-        <v>-372961.04</v>
+        <v>38361.3</v>
       </c>
       <c r="J10" s="20" t="n">
-        <v>-9615.209999999999</v>
+        <v>-82767.39</v>
       </c>
       <c r="K10" s="20" t="n">
-        <v>-764.9299999999999</v>
+        <v>10245.85</v>
       </c>
       <c r="L10" s="21">
         <f>C10+D10</f>
@@ -1012,31 +1022,31 @@
         </is>
       </c>
       <c r="C11" s="24" t="n">
-        <v>329164.9</v>
+        <v>293985.25</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>286810.96</v>
+        <v>243281.92</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>330661.44</v>
+        <v>126567.51</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-1800</v>
+        <v>100400.24</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-43103.44</v>
+        <v>63887.59</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-4816.5</v>
+        <v>-49638.12</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>-372961.04</v>
+        <v>38361.3</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>-9615.209999999999</v>
+        <v>-82767.39</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>-764.9299999999999</v>
+        <v>10245.85</v>
       </c>
       <c r="L11" s="25">
         <f>C11+D11</f>
@@ -1062,15 +1072,33 @@
           <t>March</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="18" t="n"/>
-      <c r="E12" s="18" t="n"/>
-      <c r="F12" s="18" t="n"/>
-      <c r="G12" s="18" t="n"/>
-      <c r="H12" s="18" t="n"/>
-      <c r="I12" s="18" t="n"/>
-      <c r="J12" s="18" t="n"/>
-      <c r="K12" s="18" t="n"/>
+      <c r="C12" s="20" t="n">
+        <v>2074209.28</v>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>1721842.59</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>1169705.21</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>497180.06</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>226618.71</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>380000</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>575754</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>211694.27</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>27500</v>
+      </c>
       <c r="L12" s="21">
         <f>C12+D12</f>
         <v/>
@@ -1095,15 +1123,33 @@
           <t>March</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="18" t="n"/>
-      <c r="E13" s="18" t="n"/>
-      <c r="F13" s="18" t="n"/>
-      <c r="G13" s="18" t="n"/>
-      <c r="H13" s="18" t="n"/>
-      <c r="I13" s="18" t="n"/>
-      <c r="J13" s="18" t="n"/>
-      <c r="K13" s="18" t="n"/>
+      <c r="C13" s="20" t="n">
+        <v>-1353240.27</v>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>-1014653.5</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>-277733.64</v>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>-1708.54</v>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>-50815.45</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>0</v>
+      </c>
       <c r="L13" s="21">
         <f>C13+D13</f>
         <v/>
@@ -1128,15 +1174,33 @@
           <t>March</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="18" t="n"/>
-      <c r="G14" s="18" t="n"/>
-      <c r="H14" s="18" t="n"/>
-      <c r="I14" s="18" t="n"/>
-      <c r="J14" s="18" t="n"/>
-      <c r="K14" s="18" t="n"/>
+      <c r="C14" s="20" t="n">
+        <v>-294971.79</v>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>-236028.9</v>
+      </c>
+      <c r="E14" s="20" t="n">
+        <v>-94077.71000000001</v>
+      </c>
+      <c r="F14" s="20" t="n">
+        <v>-8656.790000000001</v>
+      </c>
+      <c r="G14" s="20" t="n">
+        <v>-101326.6</v>
+      </c>
+      <c r="H14" s="20" t="n">
+        <v>-41059.22</v>
+      </c>
+      <c r="I14" s="20" t="n">
+        <v>-1635.76</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>-35413.52</v>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>-15460.83</v>
+      </c>
       <c r="L14" s="21">
         <f>C14+D14</f>
         <v/>
@@ -1161,15 +1225,33 @@
           <t>March</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="18" t="n"/>
-      <c r="E15" s="18" t="n"/>
-      <c r="F15" s="18" t="n"/>
-      <c r="G15" s="18" t="n"/>
-      <c r="H15" s="18" t="n"/>
-      <c r="I15" s="18" t="n"/>
-      <c r="J15" s="18" t="n"/>
-      <c r="K15" s="18" t="n"/>
+      <c r="C15" s="20" t="n">
+        <v>375425.35</v>
+      </c>
+      <c r="D15" s="20" t="n">
+        <v>452381.69</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <v>222893.86</v>
+      </c>
+      <c r="F15" s="20" t="n">
+        <v>-173185.27</v>
+      </c>
+      <c r="G15" s="20" t="n">
+        <v>113993.95</v>
+      </c>
+      <c r="H15" s="20" t="n">
+        <v>175247.38</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>-38540.36</v>
+      </c>
+      <c r="J15" s="20" t="n">
+        <v>115837.32</v>
+      </c>
+      <c r="K15" s="20" t="n">
+        <v>12039.17</v>
+      </c>
       <c r="L15" s="21">
         <f>C15+D15</f>
         <v/>
@@ -1194,15 +1276,33 @@
           <t>March</t>
         </is>
       </c>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="22" t="n"/>
-      <c r="E16" s="22" t="n"/>
-      <c r="F16" s="22" t="n"/>
-      <c r="G16" s="22" t="n"/>
-      <c r="H16" s="22" t="n"/>
-      <c r="I16" s="22" t="n"/>
-      <c r="J16" s="22" t="n"/>
-      <c r="K16" s="22" t="n"/>
+      <c r="C16" s="24" t="n">
+        <v>375425.35</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <v>452381.69</v>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>218884.86</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>-173185.27</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>113993.95</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>175247.38</v>
+      </c>
+      <c r="I16" s="24" t="n">
+        <v>-38540.36</v>
+      </c>
+      <c r="J16" s="24" t="n">
+        <v>115837.32</v>
+      </c>
+      <c r="K16" s="24" t="n">
+        <v>12039.17</v>
+      </c>
       <c r="L16" s="25">
         <f>C16+D16</f>
         <v/>
@@ -1527,15 +1627,33 @@
           <t>April</t>
         </is>
       </c>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="18" t="n"/>
-      <c r="E22" s="18" t="n"/>
-      <c r="F22" s="18" t="n"/>
-      <c r="G22" s="18" t="n"/>
-      <c r="H22" s="18" t="n"/>
-      <c r="I22" s="18" t="n"/>
-      <c r="J22" s="18" t="n"/>
-      <c r="K22" s="18" t="n"/>
+      <c r="C22" s="20" t="n">
+        <v>2155025.12</v>
+      </c>
+      <c r="D22" s="20" t="n">
+        <v>1784252.2</v>
+      </c>
+      <c r="E22" s="20" t="n">
+        <v>1115428.11</v>
+      </c>
+      <c r="F22" s="20" t="n">
+        <v>467963.14</v>
+      </c>
+      <c r="G22" s="20" t="n">
+        <v>162929.2</v>
+      </c>
+      <c r="H22" s="20" t="n">
+        <v>220000</v>
+      </c>
+      <c r="I22" s="20" t="n">
+        <v>526600</v>
+      </c>
+      <c r="J22" s="20" t="n">
+        <v>88534.11</v>
+      </c>
+      <c r="K22" s="20" t="n">
+        <v>27500</v>
+      </c>
       <c r="L22" s="21">
         <f>C22+D22</f>
         <v/>
@@ -1560,15 +1678,33 @@
           <t>April</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
-      <c r="H23" s="18" t="n"/>
-      <c r="I23" s="18" t="n"/>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="18" t="n"/>
+      <c r="C23" s="20" t="n">
+        <v>-1464720.72</v>
+      </c>
+      <c r="D23" s="20" t="n">
+        <v>-1288046.22</v>
+      </c>
+      <c r="E23" s="20" t="n">
+        <v>-295232.49</v>
+      </c>
+      <c r="F23" s="20" t="n">
+        <v>-1585.57</v>
+      </c>
+      <c r="G23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="20" t="n">
+        <v>-50925.55</v>
+      </c>
+      <c r="K23" s="20" t="n">
+        <v>0</v>
+      </c>
       <c r="L23" s="21">
         <f>C23+D23</f>
         <v/>
@@ -1593,15 +1729,33 @@
           <t>April</t>
         </is>
       </c>
-      <c r="C24" s="18" t="n"/>
-      <c r="D24" s="18" t="n"/>
-      <c r="E24" s="18" t="n"/>
-      <c r="F24" s="18" t="n"/>
-      <c r="G24" s="18" t="n"/>
-      <c r="H24" s="18" t="n"/>
-      <c r="I24" s="18" t="n"/>
-      <c r="J24" s="18" t="n"/>
-      <c r="K24" s="18" t="n"/>
+      <c r="C24" s="20" t="n">
+        <v>-244113.76</v>
+      </c>
+      <c r="D24" s="20" t="n">
+        <v>-190247.96</v>
+      </c>
+      <c r="E24" s="20" t="n">
+        <v>-129715.81</v>
+      </c>
+      <c r="F24" s="20" t="n">
+        <v>-21212.82</v>
+      </c>
+      <c r="G24" s="20" t="n">
+        <v>-128768.57</v>
+      </c>
+      <c r="H24" s="20" t="n">
+        <v>-41453.45</v>
+      </c>
+      <c r="I24" s="20" t="n">
+        <v>-1678.14</v>
+      </c>
+      <c r="J24" s="20" t="n">
+        <v>-25831.54</v>
+      </c>
+      <c r="K24" s="20" t="n">
+        <v>-9205.02</v>
+      </c>
       <c r="L24" s="21">
         <f>C24+D24</f>
         <v/>
@@ -1626,15 +1780,33 @@
           <t>April</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" s="18" t="n"/>
-      <c r="H25" s="18" t="n"/>
-      <c r="I25" s="18" t="n"/>
-      <c r="J25" s="18" t="n"/>
-      <c r="K25" s="18" t="n"/>
+      <c r="C25" s="20" t="n">
+        <v>418709.86</v>
+      </c>
+      <c r="D25" s="20" t="n">
+        <v>262528.4</v>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>165479.81</v>
+      </c>
+      <c r="F25" s="20" t="n">
+        <v>5164.75</v>
+      </c>
+      <c r="G25" s="20" t="n">
+        <v>26297.61</v>
+      </c>
+      <c r="H25" s="20" t="n">
+        <v>50335.8</v>
+      </c>
+      <c r="I25" s="20" t="n">
+        <v>43106.61</v>
+      </c>
+      <c r="J25" s="20" t="n">
+        <v>-39654.28</v>
+      </c>
+      <c r="K25" s="20" t="n">
+        <v>18294.98</v>
+      </c>
       <c r="L25" s="21">
         <f>C25+D25</f>
         <v/>
@@ -1659,15 +1831,33 @@
           <t>April</t>
         </is>
       </c>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="22" t="n"/>
-      <c r="E26" s="22" t="n"/>
-      <c r="F26" s="22" t="n"/>
-      <c r="G26" s="22" t="n"/>
-      <c r="H26" s="22" t="n"/>
-      <c r="I26" s="22" t="n"/>
-      <c r="J26" s="22" t="n"/>
-      <c r="K26" s="22" t="n"/>
+      <c r="C26" s="24" t="n">
+        <v>418709.86</v>
+      </c>
+      <c r="D26" s="24" t="n">
+        <v>262528.4</v>
+      </c>
+      <c r="E26" s="24" t="n">
+        <v>115479.81</v>
+      </c>
+      <c r="F26" s="24" t="n">
+        <v>5164.75</v>
+      </c>
+      <c r="G26" s="24" t="n">
+        <v>15173.99</v>
+      </c>
+      <c r="H26" s="24" t="n">
+        <v>50335.8</v>
+      </c>
+      <c r="I26" s="24" t="n">
+        <v>43106.61</v>
+      </c>
+      <c r="J26" s="24" t="n">
+        <v>-39654.28</v>
+      </c>
+      <c r="K26" s="24" t="n">
+        <v>18294.98</v>
+      </c>
       <c r="L26" s="25">
         <f>C26+D26</f>
         <v/>
